--- a/modules/LandBOSSE/input/project_list.xlsx
+++ b/modules/LandBOSSE/input/project_list.xlsx
@@ -154,7 +154,7 @@
     <t>Crane breakdown fraction</t>
   </si>
   <si>
-    <t>Assignment 4</t>
+    <t>IEA_3_4MW_17</t>
   </si>
   <si>
     <t>iea36_120_project_data</t>
@@ -675,7 +675,7 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>3.37</v>
+        <v>3.370104925</v>
       </c>
       <c r="E2">
         <v>120</v>
@@ -690,25 +690,25 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5.19</v>
+        <v>9.5</v>
       </c>
       <c r="L2">
         <v>10</v>
       </c>
       <c r="M2">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="N2">
         <v>2.36</v>
       </c>
       <c r="O2">
-        <v>625817.1355840258</v>
+        <v>631575.9901473497</v>
       </c>
       <c r="P2">
         <v>191521</v>
@@ -732,10 +732,10 @@
         <v>15</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>5.614793230191363</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="Y2" t="s">
         <v>48</v>
